--- a/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99645</t>
+          <t>99666</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104592</t>
+          <t>104601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110110</t>
+          <t>110288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116895</t>
+          <t>116857</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211856</t>
+          <t>212681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220778</t>
+          <t>220579</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117967</t>
+          <t>117505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123736</t>
+          <t>123726</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134284</t>
+          <t>134833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>140124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254783</t>
+          <t>254986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>262638</t>
+          <t>263168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102396</t>
+          <t>101631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107229</t>
+          <t>107207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103325</t>
+          <t>103143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110228</t>
+          <t>110253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208152</t>
+          <t>208419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216421</t>
+          <t>216754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158411</t>
+          <t>158655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164616</t>
+          <t>164483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149527</t>
+          <t>148932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155644</t>
+          <t>155610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310509</t>
+          <t>311268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319043</t>
+          <t>318992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>486025</t>
+          <t>486122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496564</t>
+          <t>497056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>507201</t>
+          <t>507912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>519564</t>
+          <t>519367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997510</t>
+          <t>996915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013923</t>
+          <t>1013796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89514</t>
+          <t>89696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96247</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105962</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111799</t>
+          <t>111670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198146</t>
+          <t>197595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207161</t>
+          <t>206644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123796</t>
+          <t>123797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128361</t>
+          <t>128364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151305</t>
+          <t>150314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277122</t>
+          <t>277693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>282896</t>
+          <t>282894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98270</t>
+          <t>97857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103762</t>
+          <t>103735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112308</t>
+          <t>112007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116784</t>
+          <t>116351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212611</t>
+          <t>212028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219461</t>
+          <t>219473</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135528</t>
+          <t>134676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143096</t>
+          <t>143091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149061</t>
+          <t>149242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154299</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286928</t>
+          <t>287527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296512</t>
+          <t>296628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455118</t>
+          <t>454921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467943</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>525702</t>
+          <t>526059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>534828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985727</t>
+          <t>985710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001101</t>
+          <t>1001245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>80943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88134</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96321</t>
+          <t>95960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103199</t>
+          <t>103164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180059</t>
+          <t>180536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189831</t>
+          <t>189936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140824</t>
+          <t>141107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148469</t>
+          <t>148867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160717</t>
+          <t>161537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170600</t>
+          <t>170539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304990</t>
+          <t>305224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317508</t>
+          <t>317252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>103939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112534</t>
+          <t>112339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122765</t>
+          <t>122095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130382</t>
+          <t>130241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230023</t>
+          <t>230214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241444</t>
+          <t>241242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154178</t>
+          <t>153494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162969</t>
+          <t>163359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142850</t>
+          <t>142980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153231</t>
+          <t>153302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300210</t>
+          <t>301289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314572</t>
+          <t>314738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65880</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490117</t>
+          <t>489714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506655</t>
+          <t>505839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534318</t>
+          <t>533798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551515</t>
+          <t>551049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030543</t>
+          <t>1030797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1053714</t>
+          <t>1054838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107152</t>
+          <t>106924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>114611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130674</t>
+          <t>130866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138307</t>
+          <t>138435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>240234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251864</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31891</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176083</t>
+          <t>175642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186075</t>
+          <t>185966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>233390</t>
+          <t>232898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246519</t>
+          <t>246353</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>413657</t>
+          <t>413753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429960</t>
+          <t>430153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173925</t>
+          <t>174248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185603</t>
+          <t>185733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165258</t>
+          <t>165984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177722</t>
+          <t>177884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342891</t>
+          <t>344693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360954</t>
+          <t>360858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149131</t>
+          <t>149144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>160855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160318</t>
+          <t>161050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174442</t>
+          <t>174139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>314682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331825</t>
+          <t>331775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95484</t>
+          <t>95924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>619448</t>
+          <t>619099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>639207</t>
+          <t>638384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>705624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728902</t>
+          <t>728404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332643</t>
+          <t>1332203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362655</t>
+          <t>1362782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8276</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2443</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5543</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3743</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>114546</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>110013</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116831</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102766</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>99666</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104601</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>99102</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104594</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>114546</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>110288</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116857</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>315</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212681</t>
+          <t>211906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220579</t>
+          <t>220620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6386</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3182</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7460</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2597</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5909</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>134356</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>140064</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>121783</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>117505</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123726</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>117981</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>123725</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>138145</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>134833</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>140124</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>408</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254986</t>
+          <t>254802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263168</t>
+          <t>262577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2237</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9305</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2465</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5625</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9430</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>103268</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110336</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>105383</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101631</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107207</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102223</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>107231</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>107835</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>103143</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>110253</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208419</t>
+          <t>208166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216754</t>
+          <t>216782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7508</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2910</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6681</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6884</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8014</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153576</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149438</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155649</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162426</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158655</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>164483</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158452</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>164659</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153576</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148932</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>155610</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311268</t>
+          <t>311003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318992</t>
+          <t>319000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21718</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6303</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17237</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17028</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9182</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20637</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>514100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>506831</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>519231</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>729</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>492359</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>486122</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>497056</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>486331</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>496484</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>514100</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>507912</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>519367</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996915</t>
+          <t>997718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013796</t>
+          <t>1013689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7433</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7409</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109633</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105822</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111818</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>93901</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>89696</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>96384</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>89113</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>96394</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109633</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>105092</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>111670</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197595</t>
+          <t>198207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>206644</t>
+          <t>206733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1923</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5088</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4242</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>153909</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>151322</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>127060</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>123797</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>128364</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>123895</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>128362</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>153909</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>150314</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>418</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277693</t>
+          <t>277723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>282894</t>
+          <t>282901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4773</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3053</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1116</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115034</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>112011</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>116359</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>101798</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97857</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>103735</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98177</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>104164</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115034</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>112007</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>116351</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212028</t>
+          <t>212823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>219473</t>
+          <t>219455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5828</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5982</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11326</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11296</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5699</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149113</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154297</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>140020</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>134676</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>143091</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>134706</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>143106</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>152806</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>149242</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154294</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287527</t>
+          <t>286703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296628</t>
+          <t>296624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12897</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8788</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22044</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9196</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21670</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>12722</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>531381</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>525884</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>535198</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>667</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>462780</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>454921</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>468177</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>455295</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>467769</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>531381</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>526059</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>534828</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985710</t>
+          <t>984791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001245</t>
+          <t>1000311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9027</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4625</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9142</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9071</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8714</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100689</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95647</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>103189</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>85460</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80943</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88119</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81014</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88185</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>100689</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95960</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>103164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180536</t>
+          <t>180432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189936</t>
+          <t>190058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8599</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4621</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14183</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6574</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10820</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11703</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8599</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13766</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>21992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>166704</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>161120</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>170682</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>145353</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>141107</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148867</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>140224</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>148567</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>166704</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>161537</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>170539</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>305224</t>
+          <t>305238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317252</t>
+          <t>317124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10125</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7616</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4213</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12613</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12676</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5423</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10752</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127424</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>122722</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>130183</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>108936</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>103939</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>112339</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>103876</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112429</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127424</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>122095</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>130241</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230214</t>
+          <t>230238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241242</t>
+          <t>241084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4664</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14973</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7474</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3468</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13333</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3603</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12711</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9080</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15228</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149128</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143235</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153544</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>159353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>153494</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163359</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>154116</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>163224</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>149128</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>142980</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>153302</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301289</t>
+          <t>299463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314738</t>
+          <t>313920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20042</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>36656</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19551</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35676</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35472</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>37235</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>66358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>543946</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>534377</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>550991</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>499101</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>489714</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>505839</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>489918</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>506048</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>543946</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>533798</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>551049</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1030797</t>
+          <t>1030065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1054838</t>
+          <t>1053087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4597</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9866</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10356</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121309</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>116040</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123858</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>111732</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>106924</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>114611</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135614</t>
+          <t>115240</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130866</t>
+          <t>110068</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>138435</t>
+          <t>118036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>247346</t>
+          <t>236549</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240234</t>
+          <t>230631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251674</t>
+          <t>240777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14350</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8861</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21409</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8314</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14870</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>215797</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>228345</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>182198</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>175642</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185966</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>240827</t>
+          <t>175670</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232898</t>
+          <t>169975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246353</t>
+          <t>179848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>423026</t>
+          <t>398526</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>413753</t>
+          <t>387355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430153</t>
+          <t>405096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11159</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18279</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4668</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16153</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>29347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157182</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150062</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161576</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>180567</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>174248</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>185733</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172950</t>
+          <t>147113</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165984</t>
+          <t>140934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177884</t>
+          <t>151350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>353518</t>
+          <t>304294</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344693</t>
+          <t>296044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360858</t>
+          <t>310847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12221</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19625</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12366</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7107</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18818</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>157155</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149751</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162594</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>155596</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149144</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>168725</t>
+          <t>154337</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161050</t>
+          <t>146857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174139</t>
+          <t>159222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>324322</t>
+          <t>311492</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314682</t>
+          <t>300828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331775</t>
+          <t>318896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31498</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55840</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36062</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>27771</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47056</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56348</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65345</t>
+          <t>65216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>95923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>658501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>644989</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>669331</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>888</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>630093</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>619099</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>638384</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>917</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>718117</t>
+          <t>592359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705624</t>
+          <t>581566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728404</t>
+          <t>601493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1348211</t>
+          <t>1250862</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332203</t>
+          <t>1234585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362782</t>
+          <t>1265292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
